--- a/applications/MICROSAMPLING_study/negative/neg_lipid_reference_set.xlsx
+++ b/applications/MICROSAMPLING_study/negative/neg_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/negative/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/MICROSAMPLING_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE69B414-2B08-EF4A-9511-3CABD411A755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B394921-6BA5-0C45-9AEE-0CEE71B678B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17040" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14720" windowHeight="17400" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
     <t>PC_2</t>
   </si>
   <si>
-    <t>ISTD</t>
+    <t>IS</t>
   </si>
 </sst>
 </file>
